--- a/artfynd/A 22685-2025 artfynd.xlsx
+++ b/artfynd/A 22685-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -809,6 +809,146 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>126030943</v>
+      </c>
+      <c r="B3" t="n">
+        <v>56540</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>206002</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Brunlångöra</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Plecotus auritus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Stående stor död sälg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>483188</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6664357</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>21:46</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>21:46</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ljudupptagning av Brunlångöra (Plecotus auritus) vid boträd i gammal stående död sälg. Artbestämning / verifierad av Emily Macgregor vid Naturcentrum.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Gräsblandskog</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Boplats i stående död sälg med lång kontinuitet</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22685-2025 artfynd.xlsx
+++ b/artfynd/A 22685-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -812,37 +812,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126030943</v>
+        <v>126030966</v>
       </c>
       <c r="B3" t="n">
-        <v>56540</v>
+        <v>56526</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>206002</v>
+        <v>205992</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -853,7 +853,11 @@
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stående stor död sälg, Dlr</t>
@@ -890,65 +894,678 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>23:11</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>23:11</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ljudupptagning av vattenfladdermus. Artbestämning / verifiering utförd av Emily Macgregor vid Naturcentrum.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>Boplats vid gammal stående död sälg</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Salix caprea # Boplats vid gammal stående död sälg</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>126030975</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56519</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Stående stor död sälg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>483188</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6664357</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>23:20</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>23:20</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ljudupptagning av Nordfladdermus nära boplats. Artbestämning verifierad av Emily Macgregor vid Naturcentrum. Boplats troligtvis i gammal grov rönn.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>126030943</v>
+      </c>
+      <c r="B5" t="n">
+        <v>56540</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>206002</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Brunlångöra</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Plecotus auritus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Stående stor död sälg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>483188</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6664357</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
           <t>2025-06-16</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>21:46</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-16</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>21:46</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>Ljudupptagning av Brunlångöra (Plecotus auritus) vid boträd i gammal stående död sälg. Artbestämning / verifierad av Emily Macgregor vid Naturcentrum.</t>
         </is>
       </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
         <is>
           <t>Gräsblandskog</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
+      <c r="AI5" t="inlineStr">
         <is>
           <t>Boplats i stående död sälg med lång kontinuitet</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
+      <c r="AJ5" t="inlineStr">
         <is>
           <t>sälg</t>
         </is>
       </c>
-      <c r="AK3" t="inlineStr">
+      <c r="AK5" t="inlineStr">
         <is>
           <t>Salix caprea</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
+      <c r="AO5" t="inlineStr">
         <is>
           <t>Salix caprea</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126030986</v>
+      </c>
+      <c r="B6" t="n">
+        <v>56543</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>206000</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gråskimlig fladdermus</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Vespertilio murinus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Stående stor död sälg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>483188</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6664357</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>01:20</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>01:20</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ljudupptagning av revirläte från Gråskimlig fladdermus (Vespertilio murinus) vid flera stående döda träd i äldre betesmark omgiven av blandskog. Artbestämning verifierad av Emily Macgregor vid Naturcentrum.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>Grov äldre halvdöd rönn</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia # Grov äldre halvdöd rönn</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126030959</v>
+      </c>
+      <c r="B7" t="n">
+        <v>56524</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>205988</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tajgafladdermus</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Myotis brandtii</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Eversmann, 1845)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Stående stor död sälg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>483188</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6664357</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>22:20</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>22:20</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ljudupptagning av Tajgafladdermus med bredspektrum-ultraljudinspelning vid boplats i stående död sälg. Artbestämning / verifierad observation av Emily Macgregor vid Naturcentrum.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>Födosök runt gammal stående död sälg (boplats)</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Salix caprea # Födosök runt gammal stående död sälg (boplats)</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22685-2025 artfynd.xlsx
+++ b/artfynd/A 22685-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1567,6 +1567,361 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126066371</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57811</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Sumpskog nedan ekonomibyggnader, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>483266</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6664386</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>126066185</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57809</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Sumpskog nedan ekonomibyggnader, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>483266</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6664386</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126066837</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57473</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>102976</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tornseglare</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Apus apus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Sumpskog nedan ekonomibyggnader, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>483266</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6664386</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Egil Borgne</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22685-2025 artfynd.xlsx
+++ b/artfynd/A 22685-2025 artfynd.xlsx
@@ -1569,10 +1569,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126066371</v>
+        <v>126066185</v>
       </c>
       <c r="B8" t="n">
-        <v>57811</v>
+        <v>57809</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1580,21 +1580,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>103020</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1642,22 +1642,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1689,10 +1689,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126066185</v>
+        <v>126066371</v>
       </c>
       <c r="B9" t="n">
-        <v>57809</v>
+        <v>57811</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1700,21 +1700,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103020</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1762,22 +1762,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>02:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>02:30</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 22685-2025 artfynd.xlsx
+++ b/artfynd/A 22685-2025 artfynd.xlsx
@@ -815,7 +815,7 @@
         <v>126030966</v>
       </c>
       <c r="B3" t="n">
-        <v>56526</v>
+        <v>56527</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126030975</v>
       </c>
       <c r="B4" t="n">
-        <v>56519</v>
+        <v>56520</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>126030943</v>
       </c>
       <c r="B5" t="n">
-        <v>56540</v>
+        <v>56541</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>126030986</v>
       </c>
       <c r="B6" t="n">
-        <v>56543</v>
+        <v>56544</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>126030959</v>
       </c>
       <c r="B7" t="n">
-        <v>56524</v>
+        <v>56525</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1569,10 +1569,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126066185</v>
+        <v>126066371</v>
       </c>
       <c r="B8" t="n">
-        <v>57809</v>
+        <v>57812</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1580,21 +1580,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103020</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1642,22 +1642,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>02:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>02:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1689,10 +1689,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126066371</v>
+        <v>126066185</v>
       </c>
       <c r="B9" t="n">
-        <v>57811</v>
+        <v>57810</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1700,21 +1700,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>103020</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1762,22 +1762,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1812,7 +1812,7 @@
         <v>126066837</v>
       </c>
       <c r="B10" t="n">
-        <v>57473</v>
+        <v>57474</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 22685-2025 artfynd.xlsx
+++ b/artfynd/A 22685-2025 artfynd.xlsx
@@ -1569,10 +1569,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126066371</v>
+        <v>126066185</v>
       </c>
       <c r="B8" t="n">
-        <v>57812</v>
+        <v>57810</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1580,21 +1580,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>103020</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1642,22 +1642,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1689,10 +1689,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126066185</v>
+        <v>126066371</v>
       </c>
       <c r="B9" t="n">
-        <v>57810</v>
+        <v>57812</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1700,21 +1700,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103020</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1762,22 +1762,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>02:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>02:30</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 22685-2025 artfynd.xlsx
+++ b/artfynd/A 22685-2025 artfynd.xlsx
@@ -815,7 +815,7 @@
         <v>126030966</v>
       </c>
       <c r="B3" t="n">
-        <v>56527</v>
+        <v>56531</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126030975</v>
       </c>
       <c r="B4" t="n">
-        <v>56520</v>
+        <v>56524</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>126030943</v>
       </c>
       <c r="B5" t="n">
-        <v>56541</v>
+        <v>56545</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>126030986</v>
       </c>
       <c r="B6" t="n">
-        <v>56544</v>
+        <v>56548</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>126030959</v>
       </c>
       <c r="B7" t="n">
-        <v>56525</v>
+        <v>56529</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1569,10 +1569,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126066185</v>
+        <v>126066371</v>
       </c>
       <c r="B8" t="n">
-        <v>57810</v>
+        <v>57816</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1580,21 +1580,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103020</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1642,22 +1642,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>02:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>02:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1689,10 +1689,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126066371</v>
+        <v>126066185</v>
       </c>
       <c r="B9" t="n">
-        <v>57812</v>
+        <v>57814</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1700,21 +1700,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>103020</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1762,22 +1762,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1812,7 +1812,7 @@
         <v>126066837</v>
       </c>
       <c r="B10" t="n">
-        <v>57474</v>
+        <v>57478</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 22685-2025 artfynd.xlsx
+++ b/artfynd/A 22685-2025 artfynd.xlsx
@@ -1569,10 +1569,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126066371</v>
+        <v>126066185</v>
       </c>
       <c r="B8" t="n">
-        <v>57816</v>
+        <v>57814</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1580,21 +1580,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>103020</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1642,22 +1642,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1689,10 +1689,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126066185</v>
+        <v>126066371</v>
       </c>
       <c r="B9" t="n">
-        <v>57814</v>
+        <v>57816</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1700,21 +1700,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103020</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1762,22 +1762,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>02:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>02:30</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 22685-2025 artfynd.xlsx
+++ b/artfynd/A 22685-2025 artfynd.xlsx
@@ -815,7 +815,7 @@
         <v>126030966</v>
       </c>
       <c r="B3" t="n">
-        <v>56531</v>
+        <v>56532</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126030975</v>
       </c>
       <c r="B4" t="n">
-        <v>56524</v>
+        <v>56525</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>126030943</v>
       </c>
       <c r="B5" t="n">
-        <v>56545</v>
+        <v>56546</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>126030986</v>
       </c>
       <c r="B6" t="n">
-        <v>56548</v>
+        <v>56549</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>126030959</v>
       </c>
       <c r="B7" t="n">
-        <v>56529</v>
+        <v>56530</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>126066185</v>
       </c>
       <c r="B8" t="n">
-        <v>57814</v>
+        <v>57815</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>126066371</v>
       </c>
       <c r="B9" t="n">
-        <v>57816</v>
+        <v>57817</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>126066837</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>57479</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 22685-2025 artfynd.xlsx
+++ b/artfynd/A 22685-2025 artfynd.xlsx
@@ -1268,7 +1268,7 @@
         <v>126030986</v>
       </c>
       <c r="B6" t="n">
-        <v>56549</v>
+        <v>56613</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 22685-2025 artfynd.xlsx
+++ b/artfynd/A 22685-2025 artfynd.xlsx
@@ -1268,7 +1268,7 @@
         <v>126030986</v>
       </c>
       <c r="B6" t="n">
-        <v>56613</v>
+        <v>56615</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 22685-2025 artfynd.xlsx
+++ b/artfynd/A 22685-2025 artfynd.xlsx
@@ -1268,7 +1268,7 @@
         <v>126030986</v>
       </c>
       <c r="B6" t="n">
-        <v>56615</v>
+        <v>56617</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 22685-2025 artfynd.xlsx
+++ b/artfynd/A 22685-2025 artfynd.xlsx
@@ -1418,7 +1418,7 @@
         <v>126030959</v>
       </c>
       <c r="B7" t="n">
-        <v>56530</v>
+        <v>56603</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1426,23 +1426,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>205988</v>
+        <v>232474</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tajgafladdermus</t>
+          <t>Mustaschfladdermus/tajgafladdermus</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Myotis brandtii</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Eversmann, 1845)</t>
-        </is>
-      </c>
+          <t>Myotis mystacinus/brandtii</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>1</t>

--- a/artfynd/A 22685-2025 artfynd.xlsx
+++ b/artfynd/A 22685-2025 artfynd.xlsx
@@ -1268,7 +1268,7 @@
         <v>126030986</v>
       </c>
       <c r="B6" t="n">
-        <v>56617</v>
+        <v>56620</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>126030959</v>
       </c>
       <c r="B7" t="n">
-        <v>56603</v>
+        <v>56606</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 22685-2025 artfynd.xlsx
+++ b/artfynd/A 22685-2025 artfynd.xlsx
@@ -1268,7 +1268,7 @@
         <v>126030986</v>
       </c>
       <c r="B6" t="n">
-        <v>56620</v>
+        <v>56625</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>126030959</v>
       </c>
       <c r="B7" t="n">
-        <v>56606</v>
+        <v>56611</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 22685-2025 artfynd.xlsx
+++ b/artfynd/A 22685-2025 artfynd.xlsx
@@ -1268,7 +1268,7 @@
         <v>126030986</v>
       </c>
       <c r="B6" t="n">
-        <v>56625</v>
+        <v>56626</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>126030959</v>
       </c>
       <c r="B7" t="n">
-        <v>56611</v>
+        <v>56612</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 22685-2025 artfynd.xlsx
+++ b/artfynd/A 22685-2025 artfynd.xlsx
@@ -1268,7 +1268,7 @@
         <v>126030986</v>
       </c>
       <c r="B6" t="n">
-        <v>56626</v>
+        <v>56629</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>126030959</v>
       </c>
       <c r="B7" t="n">
-        <v>56612</v>
+        <v>56615</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 22685-2025 artfynd.xlsx
+++ b/artfynd/A 22685-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>98349311</v>
+        <v>63561956</v>
       </c>
       <c r="B2" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80342</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,57 +686,47 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>2080</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skorpgelélav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rostania occultata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bagl.) Otálora, P.M.Jørg. &amp; Wedin</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rifallet södra manen, Tallbacken, Nittkvarn, Dlr</t>
+          <t>Rifallet skolan, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483165.9745121703</v>
+        <v>483145</v>
       </c>
       <c r="R2" t="n">
-        <v>6664294.556700548</v>
+        <v>6664290</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,27 +750,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:05</t>
+          <t>2017-02-12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Stor spillkråka, i stående död björk och tall. Födosökande.</t>
+          <t>2017-02-12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,26 +766,56 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Trädgård</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>trädrad med 4 lönnar</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>skogslönn</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Acer platanoides</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Henrik Jonestrand</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Henrik Jonestrand</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126030966</v>
+        <v>98349311</v>
       </c>
       <c r="B3" t="n">
-        <v>56532</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -823,51 +823,54 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205992</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>adult</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>autobox</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stående stor död sälg, Dlr</t>
+          <t>Rifallet södra manen, Tallbacken, Nittkvarn, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483188</v>
+        <v>483165</v>
       </c>
       <c r="R3" t="n">
-        <v>6664357</v>
+        <v>6664294</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -894,27 +897,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2022-01-01</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>23:11</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2022-01-01</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>23:11</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ljudupptagning av vattenfladdermus. Artbestämning / verifiering utförd av Emily Macgregor vid Naturcentrum.</t>
+          <t>Stor spillkråka, i stående död björk och tall. Födosökande.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,99 +928,69 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>Boplats vid gammal stående död sälg</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Salix caprea # Boplats vid gammal stående död sälg</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Egil Borgne</t>
+          <t>Henrik Jonestrand</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Egil Borgne</t>
+          <t>Henrik Jonestrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126030975</v>
+        <v>126066837</v>
       </c>
       <c r="B4" t="n">
-        <v>56525</v>
+        <v>57774</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>205998</v>
+        <v>102976</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>autobox</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stående stor död sälg, Dlr</t>
+          <t>Sumpskog nedan ekonomibyggnader, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483188</v>
+        <v>483266</v>
       </c>
       <c r="R4" t="n">
-        <v>6664357</v>
+        <v>6664386</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1044,27 +1017,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>23:20</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>23:20</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ljudupptagning av Nordfladdermus nära boplats. Artbestämning verifierad av Emily Macgregor vid Naturcentrum. Boplats troligtvis i gammal grov rönn.</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1075,26 +1043,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1111,10 +1059,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126030943</v>
+        <v>126066185</v>
       </c>
       <c r="B5" t="n">
-        <v>56546</v>
+        <v>58112</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,16 +1070,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>206002</v>
+        <v>103020</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1144,29 +1092,20 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>autobox</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stående stor död sälg, Dlr</t>
+          <t>Sumpskog nedan ekonomibyggnader, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483188</v>
+        <v>483266</v>
       </c>
       <c r="R5" t="n">
-        <v>6664357</v>
+        <v>6664386</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1193,27 +1132,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>21:46</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>21:46</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ljudupptagning av Brunlångöra (Plecotus auritus) vid boträd i gammal stående död sälg. Artbestämning / verifierad av Emily Macgregor vid Naturcentrum.</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1227,27 +1161,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Gräsblandskog</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Boplats i stående död sälg med lång kontinuitet</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
+          <t>Barr-/lövbland</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1265,32 +1179,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126030986</v>
+        <v>126066371</v>
       </c>
       <c r="B6" t="n">
-        <v>56629</v>
+        <v>58114</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>206000</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gråskimlig fladdermus</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Vespertilio murinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1298,25 +1212,20 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>autobox</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stående stor död sälg, Dlr</t>
+          <t>Sumpskog nedan ekonomibyggnader, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483188</v>
+        <v>483266</v>
       </c>
       <c r="R6" t="n">
-        <v>6664357</v>
+        <v>6664386</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1343,27 +1252,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>01:20</t>
+          <t>02:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>01:20</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ljudupptagning av revirläte från Gråskimlig fladdermus (Vespertilio murinus) vid flera stående döda träd i äldre betesmark omgiven av blandskog. Artbestämning verifierad av Emily Macgregor vid Naturcentrum.</t>
+          <t>02:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1378,26 +1282,6 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Barr-/lövbland</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>Grov äldre halvdöd rönn</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia # Grov äldre halvdöd rönn</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1415,10 +1299,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126030959</v>
+        <v>126030966</v>
       </c>
       <c r="B7" t="n">
-        <v>56615</v>
+        <v>56823</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1426,22 +1310,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>232474</v>
+        <v>205992</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mustaschfladdermus/tajgafladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Myotis mystacinus/brandtii</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Myotis daubentonii</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Kuhl, 1817)</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -1493,27 +1381,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>22:20</t>
+          <t>23:11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>22:20</t>
+          <t>23:11</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ljudupptagning av Tajgafladdermus med bredspektrum-ultraljudinspelning vid boplats i stående död sälg. Artbestämning / verifierad observation av Emily Macgregor vid Naturcentrum.</t>
+          <t>Ljudupptagning av vattenfladdermus. Artbestämning / verifiering utförd av Emily Macgregor vid Naturcentrum.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1527,7 +1415,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Barr-/lövbland</t>
+          <t>Blandskog</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -1542,12 +1430,12 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>Födosök runt gammal stående död sälg (boplats)</t>
+          <t>Boplats vid gammal stående död sälg</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Salix caprea # Födosök runt gammal stående död sälg (boplats)</t>
+          <t>Salix caprea # Boplats vid gammal stående död sälg</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1565,10 +1453,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126066185</v>
+        <v>126030975</v>
       </c>
       <c r="B8" t="n">
-        <v>57815</v>
+        <v>56816</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1576,42 +1464,47 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103020</v>
+        <v>205998</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sumpskog nedan ekonomibyggnader, Dlr</t>
+          <t>Stående stor död sälg, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483266</v>
+        <v>483188</v>
       </c>
       <c r="R8" t="n">
-        <v>6664386</v>
+        <v>6664357</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1638,22 +1531,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>23:20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>23:20</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ljudupptagning av Nordfladdermus nära boplats. Artbestämning verifierad av Emily Macgregor vid Naturcentrum. Boplats troligtvis i gammal grov rönn.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1668,6 +1566,21 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1685,32 +1598,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126066371</v>
+        <v>126030986</v>
       </c>
       <c r="B9" t="n">
-        <v>57817</v>
+        <v>56840</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>206000</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gråskimlig fladdermus</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Vespertilio murinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1718,20 +1631,25 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sumpskog nedan ekonomibyggnader, Dlr</t>
+          <t>Stående stor död sälg, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483266</v>
+        <v>483188</v>
       </c>
       <c r="R9" t="n">
-        <v>6664386</v>
+        <v>6664357</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1758,22 +1676,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>01:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>01:20</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ljudupptagning av revirläte från Gråskimlig fladdermus (Vespertilio murinus) vid flera stående döda träd i äldre betesmark omgiven av blandskog. Artbestämning verifierad av Emily Macgregor vid Naturcentrum.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1788,6 +1711,26 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>Grov äldre halvdöd rönn</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia # Grov äldre halvdöd rönn</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1805,27 +1748,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126066837</v>
+        <v>126030943</v>
       </c>
       <c r="B10" t="n">
-        <v>57479</v>
+        <v>56837</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102976</v>
+        <v>206002</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1835,23 +1778,32 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sumpskog nedan ekonomibyggnader, Dlr</t>
+          <t>Stående stor död sälg, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483266</v>
+        <v>483188</v>
       </c>
       <c r="R10" t="n">
-        <v>6664386</v>
+        <v>6664357</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1878,22 +1830,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>21:46</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>21:46</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ljudupptagning av Brunlångöra (Plecotus auritus) vid boträd i gammal stående död sälg. Artbestämning / verifierad av Emily Macgregor vid Naturcentrum.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1904,6 +1861,31 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Gräsblandskog</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Boplats i stående död sälg med lång kontinuitet</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
